--- a/data/argentina/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1126"/>
+  <dimension ref="A1:C1143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17352,6 +17352,275 @@
         <v>302</v>
       </c>
     </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trucco s 
+  arg </t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio centenario ciudad de quilmes
+  quilmes </t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose dellagiovanna
+  buenos aires </t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jorge luis hirschi
+  la plata </t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio florencio sola
+  buenos aires </t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio presidente peron
+  cordoba </t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio unico madre de ciudades
+  santiago del estero </t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio monumental
+  buenos aires </t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio juan bautista gargantini
+  mendoza </t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio gigante de arroyito
+  rosario </t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio pedro bidegain
+  buenos aires </t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio juan domingo peron
+  avellaneda </t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio julio cesar villagra
+  cordoba </t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">claudio fabian tapia
+  barracas </t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>UL3R30aD</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>KAydqpwC</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>nozaSkhA</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
